--- a/data/analysis/research_breadth_profiles.xlsx
+++ b/data/analysis/research_breadth_profiles.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2302,37 +2302,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>04_MUHAMMAD_FARRUKH</t>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Muhammad Farrukh Qureshi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Artificial Intelligence</t>
+          <t>Robotics &amp; Automation</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>47.8</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="G31" t="n">
-        <v>1.446</v>
+        <v>1.242</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Interdisciplinary</t>
+          <t>Focused Researcher</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2342,52 +2342,52 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>{"Machine Learning &amp; Artificial Intelligence": 47.8, "Computer Vision &amp; Image Processing": 17.4, "General Computer Science / Other": 17.4, "Biomedical &amp; Health Informatics": 8.7, "Energy &amp; Renewable Systems": 4.3, "Robotics &amp; Automation": 4.3}</t>
+          <t>{"Robotics &amp; Automation": 50.0, "Biomedical &amp; Health Informatics": 16.7, "General Computer Science / Other": 16.7, "Computer Vision &amp; Image Processing": 16.7}</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>[{"year": 2019, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2}}, {"year": 2021, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Robotics &amp; Automation": 1}}, {"year": 2023, "publication_count": 8, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"General Computer Science / Other": 2, "Machine Learning &amp; Artificial Intelligence": 3, "Energy &amp; Renewable Systems": 1, "Computer Vision &amp; Image Processing": 1, "Biomedical &amp; Health Informatics": 1}}, {"year": 2024, "publication_count": 5, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Biomedical &amp; Health Informatics": 1, "Computer Vision &amp; Image Processing": 2}}, {"year": 2025, "publication_count": 4, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 3, "Computer Vision &amp; Image Processing": 1}}]</t>
+          <t>[{"year": 2025, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2026, "publication_count": 4, "dominant_theme": "Robotics &amp; Automation", "theme_counts": {"Computer Vision &amp; Image Processing": 1, "Robotics &amp; Automation": 3}}]</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Farrukh Qureshi has authored 23 publication(s) across 6 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 47.8% of all publications. With a normalized diversity score of 0.81, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate nan has authored 6 publication(s) across 4 research theme(s). The primary research concentration is in Robotics &amp; Automation, accounting for 50.0% of all publications. With a normalized diversity score of 0.90, the overall research profile is classified as Focused Researcher.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Interdisciplinary</t>
+          <t>Focused Researcher</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11_WAQAS_AMIN</t>
+          <t>04_MUHAMMAD_FARRUKH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Waqas Amin</t>
+          <t>Muhammad Farrukh Qureshi</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Energy &amp; Renewable Systems</t>
+          <t>Machine Learning &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>44</v>
+        <v>47.8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1.432</v>
+        <v>1.446</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>{"Energy &amp; Renewable Systems": 44.0, "Cybersecurity &amp; Privacy": 28.0, "Machine Learning &amp; Artificial Intelligence": 12.0, "General Computer Science / Other": 8.0, "Natural Language Processing": 4.0, "Wireless Networks &amp; IoT": 4.0}</t>
+          <t>{"Machine Learning &amp; Artificial Intelligence": 47.8, "Computer Vision &amp; Image Processing": 17.4, "General Computer Science / Other": 17.4, "Biomedical &amp; Health Informatics": 8.7, "Energy &amp; Renewable Systems": 4.3, "Robotics &amp; Automation": 4.3}</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>[{"year": 2019, "publication_count": 1, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1}}, {"year": 2020, "publication_count": 5, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 3, "Cybersecurity &amp; Privacy": 1, "General Computer Science / Other": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 2}}, {"year": 2024, "publication_count": 2, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2025, "publication_count": 12, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Natural Language Processing": 1, "Machine Learning &amp; Artificial Intelligence": 3, "Cybersecurity &amp; Privacy": 2, "Energy &amp; Renewable Systems": 4, "General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 1}}]</t>
+          <t>[{"year": 2019, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2}}, {"year": 2021, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Robotics &amp; Automation": 1}}, {"year": 2023, "publication_count": 8, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"General Computer Science / Other": 2, "Machine Learning &amp; Artificial Intelligence": 3, "Energy &amp; Renewable Systems": 1, "Computer Vision &amp; Image Processing": 1, "Biomedical &amp; Health Informatics": 1}}, {"year": 2024, "publication_count": 5, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Biomedical &amp; Health Informatics": 1, "Computer Vision &amp; Image Processing": 2}}, {"year": 2025, "publication_count": 4, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 3, "Computer Vision &amp; Image Processing": 1}}]</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Candidate Waqas Amin has authored 25 publication(s) across 6 research theme(s). The primary research concentration is in Energy &amp; Renewable Systems, accounting for 44.0% of all publications. With a normalized diversity score of 0.80, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Muhammad Farrukh Qureshi has authored 23 publication(s) across 6 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 47.8% of all publications. With a normalized diversity score of 0.81, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2426,33 +2426,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13_MANZOOR_ELLAHI</t>
+          <t>09_SANA_FATIMA_RIZVI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Manzoor Ellahi</t>
+          <t>Sana Fatima Rizvi</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>General Computer Science / Other</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>39.1</v>
+        <v>33.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.826</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1.48</v>
+        <v>1.099</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>{"General Computer Science / Other": 39.1, "Energy &amp; Renewable Systems": 30.4, "Machine Learning &amp; Artificial Intelligence": 13.0, "Wireless Networks &amp; IoT": 8.7, "Biomedical &amp; Health Informatics": 4.3, "Natural Language Processing": 4.3}</t>
+          <t>{"Natural Language Processing": 33.3, "Cybersecurity &amp; Privacy": 33.3, "Biomedical &amp; Health Informatics": 33.3}</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>[{"year": 2013, "publication_count": 2, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 1, "General Computer Science / Other": 1}}, {"year": 2017, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "General Computer Science / Other": 1}}, {"year": 2018, "publication_count": 5, "dominant_theme": "General Computer Science / Other", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Natural Language Processing": 1, "General Computer Science / Other": 3}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 2}}, {"year": 2020, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "General Computer Science / Other": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2, "Energy &amp; Renewable Systems": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Energy &amp; Renewable Systems": 1, "Wireless Networks &amp; IoT": 1}}, {"year": 2025, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}]</t>
+          <t>[{"year": 2022, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1}}, {"year": 2024, "publication_count": 1, "dominant_theme": "Natural Language Processing", "theme_counts": {"Natural Language Processing": 1}}]</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Candidate Manzoor Ellahi has authored 23 publication(s) across 6 research theme(s). The primary research concentration is in General Computer Science / Other, accounting for 39.1% of all publications. With a normalized diversity score of 0.83, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Sana Fatima Rizvi has authored 3 publication(s) across 3 research theme(s). The primary research concentration is in Natural Language Processing, accounting for 33.3% of all publications. With a normalized diversity score of 1.00, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2488,34 +2488,34 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>16_MUZZAMIL_GHAFFAR</t>
+          <t>11_WAQAS_AMIN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Muzzamil Ghaffar</t>
+          <t>Waqas Amin</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>25</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Energy &amp; Renewable Systems</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>44</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="H34" t="n">
         <v>6</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4</v>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Interdisciplinary</t>
@@ -2523,22 +2523,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Shifting / Interdisciplinary Focus</t>
+          <t>Evolving Focus</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>{"Machine Learning &amp; Artificial Intelligence": 33.3, "Energy &amp; Renewable Systems": 33.3, "General Computer Science / Other": 16.7, "Biomedical &amp; Health Informatics": 16.7}</t>
+          <t>{"Energy &amp; Renewable Systems": 44.0, "Cybersecurity &amp; Privacy": 28.0, "Machine Learning &amp; Artificial Intelligence": 12.0, "General Computer Science / Other": 8.0, "Natural Language Processing": 4.0, "Wireless Networks &amp; IoT": 4.0}</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>[{"year": 2018, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 2}}, {"year": 2021, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}, {"year": 2022, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}]</t>
+          <t>[{"year": 2019, "publication_count": 1, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1}}, {"year": 2020, "publication_count": 5, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 3, "Cybersecurity &amp; Privacy": 1, "General Computer Science / Other": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 2}}, {"year": 2024, "publication_count": 2, "dominant_theme": "Cybersecurity &amp; Privacy", "theme_counts": {"Cybersecurity &amp; Privacy": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2025, "publication_count": 12, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Natural Language Processing": 1, "Machine Learning &amp; Artificial Intelligence": 3, "Cybersecurity &amp; Privacy": 2, "Energy &amp; Renewable Systems": 4, "General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 1}}]</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Candidate Muzzamil Ghaffar has authored 6 publication(s) across 4 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 33.3% of all publications. With a normalized diversity score of 0.96, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Waqas Amin has authored 25 publication(s) across 6 research theme(s). The primary research concentration is in Energy &amp; Renewable Systems, accounting for 44.0% of all publications. With a normalized diversity score of 0.80, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2550,30 +2550,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>23_WAQAS_TARIQ_TOOR</t>
+          <t>13_MANZOOR_ELLAHI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Waqas Tariq Toor</t>
+          <t>Manzoor Ellahi</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wireless Networks &amp; IoT</t>
+          <t>General Computer Science / Other</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>41.4</v>
+        <v>39.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="G35" t="n">
-        <v>1.451</v>
+        <v>1.48</v>
       </c>
       <c r="H35" t="n">
         <v>6</v>
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>{"Wireless Networks &amp; IoT": 41.4, "Machine Learning &amp; Artificial Intelligence": 24.1, "General Computer Science / Other": 20.7, "Energy &amp; Renewable Systems": 6.9, "Biomedical &amp; Health Informatics": 3.4, "Computer Vision &amp; Image Processing": 3.4}</t>
+          <t>{"General Computer Science / Other": 39.1, "Energy &amp; Renewable Systems": 30.4, "Machine Learning &amp; Artificial Intelligence": 13.0, "Wireless Networks &amp; IoT": 8.7, "Biomedical &amp; Health Informatics": 4.3, "Natural Language Processing": 4.3}</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>[{"year": 2017, "publication_count": 2, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1, "General Computer Science / Other": 1}}, {"year": 2020, "publication_count": 5, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 4}}, {"year": 2021, "publication_count": 3, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2, "General Computer Science / Other": 1}}, {"year": 2022, "publication_count": 4, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2, "Wireless Networks &amp; IoT": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 1, "Computer Vision &amp; Image Processing": 1}}, {"year": 2024, "publication_count": 6, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 5, "Energy &amp; Renewable Systems": 1}}, {"year": 2025, "publication_count": 4, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2, "Machine Learning &amp; Artificial Intelligence": 1, "Energy &amp; Renewable Systems": 1}}]</t>
+          <t>[{"year": 2013, "publication_count": 2, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 1, "General Computer Science / Other": 1}}, {"year": 2017, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "General Computer Science / Other": 1}}, {"year": 2018, "publication_count": 5, "dominant_theme": "General Computer Science / Other", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Natural Language Processing": 1, "General Computer Science / Other": 3}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 2}}, {"year": 2020, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "General Computer Science / Other": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2022, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2, "Energy &amp; Renewable Systems": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Energy &amp; Renewable Systems": 1, "Wireless Networks &amp; IoT": 1}}, {"year": 2025, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}]</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Candidate Waqas Tariq Toor has authored 29 publication(s) across 6 research theme(s). The primary research concentration is in Wireless Networks &amp; IoT, accounting for 41.4% of all publications. With a normalized diversity score of 0.81, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Manzoor Ellahi has authored 23 publication(s) across 6 research theme(s). The primary research concentration is in General Computer Science / Other, accounting for 39.1% of all publications. With a normalized diversity score of 0.83, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2612,16 +2612,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
+          <t>16_MUZZAMIL_GHAFFAR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MUHAMMAD ADEEL ALTAF</t>
+          <t>Muzzamil Ghaffar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96</v>
+        <v>0.959</v>
       </c>
       <c r="G36" t="n">
-        <v>1.055</v>
+        <v>1.33</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2647,22 +2647,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Evolving Focus</t>
+          <t>Shifting / Interdisciplinary Focus</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>{"Machine Learning &amp; Artificial Intelligence": 40.0, "General Computer Science / Other": 40.0, "Computer Vision &amp; Image Processing": 20.0}</t>
+          <t>{"Machine Learning &amp; Artificial Intelligence": 33.3, "Energy &amp; Renewable Systems": 33.3, "General Computer Science / Other": 16.7, "Biomedical &amp; Health Informatics": 16.7}</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>[{"year": 2022, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2024, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2025, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Computer Vision &amp; Image Processing": 1}}]</t>
+          <t>[{"year": 2018, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Energy &amp; Renewable Systems", "theme_counts": {"Energy &amp; Renewable Systems": 2}}, {"year": 2021, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}, {"year": 2022, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}]</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Candidate MUHAMMAD ADEEL ALTAF has authored 5 publication(s) across 3 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 40.0% of all publications. With a normalized diversity score of 0.96, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Muzzamil Ghaffar has authored 6 publication(s) across 4 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 33.3% of all publications. With a normalized diversity score of 0.96, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2674,33 +2674,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34_SHAHZAD</t>
+          <t>23_WAQAS_TARIQ_TOOR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Shahzad</t>
+          <t>Waqas Tariq Toor</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Artificial Intelligence</t>
+          <t>Wireless Networks &amp; IoT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>44.4</v>
+        <v>41.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.918</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>1.273</v>
+        <v>1.451</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2714,17 +2714,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>{"Machine Learning &amp; Artificial Intelligence": 44.4, "Wireless Networks &amp; IoT": 22.2, "General Computer Science / Other": 22.2, "Energy &amp; Renewable Systems": 11.1}</t>
+          <t>{"Wireless Networks &amp; IoT": 41.4, "Machine Learning &amp; Artificial Intelligence": 24.1, "General Computer Science / Other": 20.7, "Energy &amp; Renewable Systems": 6.9, "Biomedical &amp; Health Informatics": 3.4, "Computer Vision &amp; Image Processing": 3.4}</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>[{"year": 2019, "publication_count": 1, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 1}}, {"year": 2020, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Wireless Networks &amp; IoT": 1}}, {"year": 2022, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"General Computer Science / Other": 1, "Machine Learning &amp; Artificial Intelligence": 2}}]</t>
+          <t>[{"year": 2017, "publication_count": 2, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2}}, {"year": 2019, "publication_count": 2, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1, "General Computer Science / Other": 1}}, {"year": 2020, "publication_count": 5, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 4}}, {"year": 2021, "publication_count": 3, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2, "General Computer Science / Other": 1}}, {"year": 2022, "publication_count": 4, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 2, "Wireless Networks &amp; IoT": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 1, "Computer Vision &amp; Image Processing": 1}}, {"year": 2024, "publication_count": 6, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 5, "Energy &amp; Renewable Systems": 1}}, {"year": 2025, "publication_count": 4, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 2, "Machine Learning &amp; Artificial Intelligence": 1, "Energy &amp; Renewable Systems": 1}}]</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Candidate Shahzad has authored 9 publication(s) across 4 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 44.4% of all publications. With a normalized diversity score of 0.92, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Waqas Tariq Toor has authored 29 publication(s) across 6 research theme(s). The primary research concentration is in Wireless Networks &amp; IoT, accounting for 41.4% of all publications. With a normalized diversity score of 0.81, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2736,16 +2736,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>41_MUHAMMAD_AQEEL</t>
+          <t>25_MUHAMMAD_ADEEL_ALTAF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Muhammad Aqeel</t>
+          <t>MUHAMMAD ADEEL ALTAF</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>46.7</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="G38" t="n">
-        <v>1.488</v>
+        <v>1.055</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2771,22 +2771,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Shifting / Interdisciplinary Focus</t>
+          <t>Evolving Focus</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>{"Machine Learning &amp; Artificial Intelligence": 46.7, "Computer Vision &amp; Image Processing": 20.0, "Wireless Networks &amp; IoT": 13.3, "Biomedical &amp; Health Informatics": 6.7, "General Computer Science / Other": 6.7, "Energy &amp; Renewable Systems": 6.7}</t>
+          <t>{"Machine Learning &amp; Artificial Intelligence": 40.0, "General Computer Science / Other": 40.0, "Computer Vision &amp; Image Processing": 20.0}</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>[{"year": 2005, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2020, "publication_count": 4, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Computer Vision &amp; Image Processing": 2, "Biomedical &amp; Health Informatics": 1}}, {"year": 2023, "publication_count": 5, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 2, "Energy &amp; Renewable Systems": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 3}}, {"year": 2025, "publication_count": 2, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2}}]</t>
+          <t>[{"year": 2022, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2024, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2025, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2, "Computer Vision &amp; Image Processing": 1}}]</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Aqeel has authored 15 publication(s) across 6 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 46.7% of all publications. With a normalized diversity score of 0.83, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate MUHAMMAD ADEEL ALTAF has authored 5 publication(s) across 3 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 40.0% of all publications. With a normalized diversity score of 0.96, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2798,33 +2798,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>43_AMMARA_NASIM</t>
+          <t>34_SHAHZAD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ammara Nasim</t>
+          <t>Shahzad</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Computer Vision &amp; Image Processing</t>
+          <t>Machine Learning &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0.861</v>
+        <v>0.918</v>
       </c>
       <c r="G39" t="n">
-        <v>1.385</v>
+        <v>1.273</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2838,17 +2838,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>{"Computer Vision &amp; Image Processing": 47.1, "General Computer Science / Other": 17.6, "Biomedical &amp; Health Informatics": 17.6, "Machine Learning &amp; Artificial Intelligence": 11.8, "Natural Language Processing": 5.9}</t>
+          <t>{"Machine Learning &amp; Artificial Intelligence": 44.4, "Wireless Networks &amp; IoT": 22.2, "General Computer Science / Other": 22.2, "Energy &amp; Renewable Systems": 11.1}</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>[{"year": 2013, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2014, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2015, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}, {"year": 2017, "publication_count": 3, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 2, "Biomedical &amp; Health Informatics": 1}}, {"year": 2018, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Biomedical &amp; Health Informatics": 1}}, {"year": 2019, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2020, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Natural Language Processing": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2025, "publication_count": 3, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 3}}]</t>
+          <t>[{"year": 2019, "publication_count": 1, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Wireless Networks &amp; IoT": 1}}, {"year": 2020, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Energy &amp; Renewable Systems": 1}}, {"year": 2021, "publication_count": 2, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Wireless Networks &amp; IoT": 1}}, {"year": 2022, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"General Computer Science / Other": 1, "Machine Learning &amp; Artificial Intelligence": 2}}]</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Candidate Ammara Nasim has authored 17 publication(s) across 5 research theme(s). The primary research concentration is in Computer Vision &amp; Image Processing, accounting for 47.1% of all publications. With a normalized diversity score of 0.86, the overall research profile is classified as Interdisciplinary.</t>
+          <t>Candidate Shahzad has authored 9 publication(s) across 4 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 44.4% of all publications. With a normalized diversity score of 0.92, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2860,136 +2860,136 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02_MUHAMMAD_SHAHWAZ</t>
+          <t>41_MUHAMMAD_AQEEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MUHAMMAD SHAHWAZ</t>
+          <t>Muhammad Aqeel</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Machine Learning &amp; Artificial Intelligence</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1.488</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>No Publications</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Shifting / Interdisciplinary Focus</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Machine Learning &amp; Artificial Intelligence": 46.7, "Computer Vision &amp; Image Processing": 20.0, "Wireless Networks &amp; IoT": 13.3, "Biomedical &amp; Health Informatics": 6.7, "General Computer Science / Other": 6.7, "Energy &amp; Renewable Systems": 6.7}</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"year": 2005, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2020, "publication_count": 4, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "Computer Vision &amp; Image Processing": 2, "Biomedical &amp; Health Informatics": 1}}, {"year": 2023, "publication_count": 5, "dominant_theme": "Wireless Networks &amp; IoT", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1, "General Computer Science / Other": 1, "Wireless Networks &amp; IoT": 2, "Energy &amp; Renewable Systems": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 3}}, {"year": 2025, "publication_count": 2, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 2}}]</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Candidate 02_MUHAMMAD_SHAHWAZ has no publications listed in their CV.</t>
+          <t>Candidate Muhammad Aqeel has authored 15 publication(s) across 6 research theme(s). The primary research concentration is in Machine Learning &amp; Artificial Intelligence, accounting for 46.7% of all publications. With a normalized diversity score of 0.83, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>No Publications</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06_FARMAN_ALI</t>
+          <t>43_AMMARA_NASIM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Farman Ali</t>
+          <t>Ammara Nasim</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Computer Vision &amp; Image Processing</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.861</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.385</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No Publications</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Shifting / Interdisciplinary Focus</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Computer Vision &amp; Image Processing": 47.1, "General Computer Science / Other": 17.6, "Biomedical &amp; Health Informatics": 17.6, "Machine Learning &amp; Artificial Intelligence": 11.8, "Natural Language Processing": 5.9}</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"year": 2013, "publication_count": 1, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1}}, {"year": 2014, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2015, "publication_count": 1, "dominant_theme": "Biomedical &amp; Health Informatics", "theme_counts": {"Biomedical &amp; Health Informatics": 1}}, {"year": 2017, "publication_count": 3, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 2, "Biomedical &amp; Health Informatics": 1}}, {"year": 2018, "publication_count": 2, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Biomedical &amp; Health Informatics": 1}}, {"year": 2019, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2020, "publication_count": 1, "dominant_theme": "Machine Learning &amp; Artificial Intelligence", "theme_counts": {"Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2023, "publication_count": 1, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 1}}, {"year": 2024, "publication_count": 3, "dominant_theme": "General Computer Science / Other", "theme_counts": {"General Computer Science / Other": 1, "Natural Language Processing": 1, "Machine Learning &amp; Artificial Intelligence": 1}}, {"year": 2025, "publication_count": 3, "dominant_theme": "Computer Vision &amp; Image Processing", "theme_counts": {"Computer Vision &amp; Image Processing": 3}}]</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Candidate 06_FARMAN_ALI has no publications listed in their CV.</t>
+          <t>Candidate Ammara Nasim has authored 17 publication(s) across 5 research theme(s). The primary research concentration is in Computer Vision &amp; Image Processing, accounting for 47.1% of all publications. With a normalized diversity score of 0.86, the overall research profile is classified as Interdisciplinary.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>No Publications</t>
+          <t>Interdisciplinary</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10_MUHAMMAD_EHATISHAM</t>
+          <t>02_MUHAMMAD_SHAHWAZ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Muhammad Ehatisham</t>
+          <t>MUHAMMAD SHAHWAZ</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Candidate 10_MUHAMMAD_EHATISHAM has no publications listed in their CV.</t>
+          <t>Candidate 02_MUHAMMAD_SHAHWAZ has no publications listed in their CV.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3046,12 +3046,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27_SHAHEER</t>
+          <t>06_FARMAN_ALI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shaheer</t>
+          <t>Farman Ali</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Candidate 27_SHAHEER has no publications listed in their CV.</t>
+          <t>Candidate 06_FARMAN_ALI has no publications listed in their CV.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3108,12 +3108,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>42_SAQIB_JAMIL</t>
+          <t>10_MUHAMMAD_EHATISHAM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Saqib Jamil</t>
+          <t>Muhammad Ehatisham</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -3158,10 +3158,134 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Candidate 10_MUHAMMAD_EHATISHAM has no publications listed in their CV.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>No Publications</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>27_SHAHEER</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Shaheer</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No Publications</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Candidate 27_SHAHEER has no publications listed in their CV.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>No Publications</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>42_SAQIB_JAMIL</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Saqib Jamil</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No Publications</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
           <t>Candidate 42_SAQIB_JAMIL has no publications listed in their CV.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>No Publications</t>
         </is>
@@ -3178,7 +3302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G380"/>
+  <dimension ref="A1:G389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14857,7 +14981,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2013.0</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -14886,7 +15010,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -14919,7 +15043,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2015.0</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -14952,7 +15076,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -14981,7 +15105,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -15014,7 +15138,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -15051,7 +15175,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -15088,7 +15212,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -15125,7 +15249,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -15154,7 +15278,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -15191,7 +15315,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2023.0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -15228,7 +15352,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -15265,7 +15389,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024.0</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -15302,7 +15426,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -15335,7 +15459,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -15368,7 +15492,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025.0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -15405,27 +15529,340 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
+          <t>2025.0</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Engineering Applications of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Computer Vision &amp; Image Processing</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Transformer-Based Sentiment Analysis for Low-Resource Urdu Text</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2024.0</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>IEEE Access</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Natural Language Processing</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>sentiment, sentiment analysis, transformer</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>A Federated Learning Framework for Privacy-Preserving Healthcare Diagnostics</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2023.0</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Cybersecurity &amp; Privacy</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>privacy</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>09_SANA_FATIMA_RIZVI</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Deep Learning Approaches for Crop Disease Detection in Punjab Informatics &amp; Biomedical</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2022.0</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Journal of Computing</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>biomedical, disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Large Language Models in Clinical Reasoning: Capabilities, Challenges, and the Future of AI-Assisted Healthcare</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Journal of Healthcare Informatics Research</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>healthcare, clinical</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Bridging Performance and Efficiency: Distilling Vision Transformers for Remote Sensing</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>Engineering Applications of Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2025 5th International Conference on Digital Futures and Transformative Technologies (ICoDT2)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>General Computer Science / Other</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>From Segmentation to Structured Reports: Auditable Continual Learning for Automation in Medical Imaging Diagnostics</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026 International Conference on Robotics and Automation in Industry (ICRAI)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
         <is>
           <t>Computer Vision &amp; Image Processing</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Machine Learning &amp; Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>segmentation</t>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>segmentation, medical imaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>HunarmandAI: A Bilingual Intelligent Diagnostic Interface for Smart Vehicles and Industrial Mechatronic Systems</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026 International Conference on Robotics and Automation in Industry (ICRAI)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Automation</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>robotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>XMedFusion: A Knowledge-Guided Multimodal Perception and Reasoning Framework for Autonomous Medical Systems</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026 International Conference on Robotics and Automation in Industry (ICRAI)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Automation</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>robotics, autonomous</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Muhammad_Dawood_Rizwan_CV</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>MedLingo: Resource-Efficient Hierarchical Multi-Agent Intelligence for Autonomous Clinical and Robotic Diagnostics</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026 International Conference on Robotics and Automation in Industry (ICRAI)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Robotics &amp; Automation</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Biomedical &amp; Health Informatics</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>robotics, autonomous</t>
         </is>
       </c>
     </row>
